--- a/evaluation/final-99-gate-current-2026-07-22/orchestration-download/files/세이프건설-risk-assessment.xlsx
+++ b/evaluation/final-99-gate-current-2026-07-22/orchestration-download/files/세이프건설-risk-assessment.xlsx
@@ -259,13 +259,13 @@
     <t>- 폭염·고온 신호</t>
   </si>
   <si>
-    <t>여름철 체감온도 연결 보류</t>
+    <t>영향예보 보건(일반인) 주의 (군산옥도면(어청도 제외))</t>
   </si>
   <si>
     <t>- 자외선 신호</t>
   </si>
   <si>
-    <t>자외선지수 1 (낮음) / 실시간 홍반자외선 연결 보류</t>
+    <t>자외선지수 0 (낮음) / 실시간 홍반자외선 연결 보류</t>
   </si>
   <si>
     <t>- 유해·위험요인</t>

--- a/evaluation/final-99-gate-current-2026-07-22/orchestration-download/files/세이프건설-risk-assessment.xlsx
+++ b/evaluation/final-99-gate-current-2026-07-22/orchestration-download/files/세이프건설-risk-assessment.xlsx
@@ -259,7 +259,7 @@
     <t>- 폭염·고온 신호</t>
   </si>
   <si>
-    <t>영향예보 보건(일반인) 주의 (군산옥도면(어청도 제외))</t>
+    <t>여름철 체감온도 연결 보류</t>
   </si>
   <si>
     <t>- 자외선 신호</t>

--- a/evaluation/final-99-gate-current-2026-07-22/orchestration-download/files/세이프건설-risk-assessment.xlsx
+++ b/evaluation/final-99-gate-current-2026-07-22/orchestration-download/files/세이프건설-risk-assessment.xlsx
@@ -259,7 +259,7 @@
     <t>- 폭염·고온 신호</t>
   </si>
   <si>
-    <t>여름철 체감온도 연결 보류</t>
+    <t>영향예보 보건(일반인) 주의 (군산옥도면(어청도 제외))</t>
   </si>
   <si>
     <t>- 자외선 신호</t>
